--- a/data/trans_orig/IP04F-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP04F-Provincia-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>40797</t>
+          <t>41101</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50130</t>
+          <t>50162</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>51803</t>
+          <t>52408</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>61072</t>
+          <t>61317</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>96687</t>
+          <t>96888</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>109823</t>
+          <t>109485</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>90,85%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5570</t>
+          <t>5538</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14903</t>
+          <t>14599</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3737</t>
+          <t>3492</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13006</t>
+          <t>12401</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10686</t>
+          <t>11024</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23822</t>
+          <t>23621</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,6%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>92234</t>
+          <t>92004</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>100733</t>
+          <t>100799</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>100515</t>
+          <t>100069</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>108544</t>
+          <t>108003</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>194858</t>
+          <t>195678</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>207059</t>
+          <t>207481</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>96,11%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3980</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12479</t>
+          <t>12709</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>3156</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10644</t>
+          <t>11090</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>8813</t>
+          <t>8391</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>21014</t>
+          <t>20194</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,35%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>54600</t>
+          <t>54340</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63328</t>
+          <t>63747</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>79,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>59002</t>
+          <t>58802</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>67274</t>
+          <t>67238</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>82,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>116495</t>
+          <t>116123</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>128540</t>
+          <t>128921</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,46%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4850</t>
+          <t>4431</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13578</t>
+          <t>13838</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3980</t>
+          <t>4016</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12252</t>
+          <t>12452</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10892</t>
+          <t>10511</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>22937</t>
+          <t>23309</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,72%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>67272</t>
+          <t>67109</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>75731</t>
+          <t>75459</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>75921</t>
+          <t>75117</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>81154</t>
+          <t>81144</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>146072</t>
+          <t>146194</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>155788</t>
+          <t>155717</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,59%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>2302</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10489</t>
+          <t>10652</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>661</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5884</t>
+          <t>6688</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3778</t>
+          <t>3849</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13494</t>
+          <t>13372</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35200</t>
+          <t>35625</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41857</t>
+          <t>42495</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36918</t>
+          <t>36639</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44445</t>
+          <t>44278</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>78,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>75150</t>
+          <t>75767</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>85520</t>
+          <t>85420</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,23%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2044</t>
+          <t>1406</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8701</t>
+          <t>8276</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2307</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9834</t>
+          <t>10113</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5133</t>
+          <t>5233</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15503</t>
+          <t>14886</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,42%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>43551</t>
+          <t>44208</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>52159</t>
+          <t>52347</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>50931</t>
+          <t>50335</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>57360</t>
+          <t>57454</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>97574</t>
+          <t>98145</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>108421</t>
+          <t>108746</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,77%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3132</t>
+          <t>2944</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11740</t>
+          <t>11083</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2098</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8527</t>
+          <t>9123</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6328</t>
+          <t>6003</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>17175</t>
+          <t>16604</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,47%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>115447</t>
+          <t>116315</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>127814</t>
+          <t>128419</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>123731</t>
+          <t>124438</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>135863</t>
+          <t>135709</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>244204</t>
+          <t>245137</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>261247</t>
+          <t>260837</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,67%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9227</t>
+          <t>8622</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>21594</t>
+          <t>20726</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>8560</t>
+          <t>8714</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>20692</t>
+          <t>19985</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>20217</t>
+          <t>20627</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>37260</t>
+          <t>36327</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>12,91%</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>135708</t>
+          <t>135386</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>149063</t>
+          <t>149140</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>141563</t>
+          <t>140901</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>155373</t>
+          <t>155499</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>283241</t>
+          <t>281051</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>300505</t>
+          <t>300665</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,74%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>12389</t>
+          <t>12312</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>25744</t>
+          <t>26066</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>14534</t>
+          <t>14408</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>28344</t>
+          <t>29006</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>30854</t>
+          <t>30694</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>48118</t>
+          <t>50308</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>15,18%</t>
         </is>
       </c>
     </row>
@@ -3475,12 +3475,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>616173</t>
+          <t>616498</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>643538</t>
+          <t>642454</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3490,12 +3490,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>669599</t>
+          <t>668705</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>694777</t>
+          <t>694298</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3525,12 +3525,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1293194</t>
+          <t>1292995</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1330548</t>
+          <t>1330131</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3560,12 +3560,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,51%</t>
         </is>
       </c>
     </row>
@@ -3588,12 +3588,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>60499</t>
+          <t>61583</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>87864</t>
+          <t>87539</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3603,12 +3603,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>54791</t>
+          <t>55270</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>79969</t>
+          <t>80863</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>123057</t>
+          <t>123474</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>160411</t>
+          <t>160610</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>43590</t>
+          <t>44075</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51725</t>
+          <t>51917</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>51109</t>
+          <t>51103</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>59755</t>
+          <t>59695</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>98797</t>
+          <t>97837</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>110184</t>
+          <t>110042</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>80,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,08%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4628</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12763</t>
+          <t>12278</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4707</t>
+          <t>4767</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13353</t>
+          <t>13359</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10631</t>
+          <t>10773</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22018</t>
+          <t>22978</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>19,02%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>94913</t>
+          <t>94998</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>101533</t>
+          <t>101725</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>101015</t>
+          <t>100608</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>106834</t>
+          <t>106838</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4447,7 +4447,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>197891</t>
+          <t>198645</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>207451</t>
+          <t>207597</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,15%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1810</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8430</t>
+          <t>8345</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1328</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7151</t>
+          <t>7558</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4058</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13618</t>
+          <t>12864</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,08%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>58445</t>
+          <t>58256</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65317</t>
+          <t>65375</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>58082</t>
+          <t>58875</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>66993</t>
+          <t>67025</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>121304</t>
+          <t>119460</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>131641</t>
+          <t>130882</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>95,72%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>1456</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8386</t>
+          <t>8575</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11823</t>
+          <t>11030</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5095</t>
+          <t>5854</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>15432</t>
+          <t>17276</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>12,63%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>66410</t>
+          <t>65966</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>73350</t>
+          <t>73323</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>72446</t>
+          <t>72139</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>78448</t>
+          <t>78434</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>140923</t>
+          <t>141110</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>150334</t>
+          <t>150779</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,29%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>2485</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9398</t>
+          <t>9842</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>735</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6723</t>
+          <t>7030</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4643</t>
+          <t>4198</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14054</t>
+          <t>13867</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,95%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35706</t>
+          <t>35023</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41527</t>
+          <t>41530</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38388</t>
+          <t>38707</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44462</t>
+          <t>44509</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>76581</t>
+          <t>76631</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>85186</t>
+          <t>85208</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,22%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1336</t>
+          <t>1333</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7157</t>
+          <t>7840</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1226</t>
+          <t>1179</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7300</t>
+          <t>6981</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3365</t>
+          <t>3343</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11970</t>
+          <t>11920</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,46%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>40335</t>
+          <t>40877</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>49354</t>
+          <t>49394</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>49686</t>
+          <t>49486</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>56256</t>
+          <t>56298</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>92580</t>
+          <t>93134</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>104797</t>
+          <t>104174</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>83,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,0%</t>
         </is>
       </c>
     </row>
@@ -5882,12 +5882,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4919</t>
+          <t>4879</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13938</t>
+          <t>13396</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1483</t>
+          <t>1441</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8053</t>
+          <t>8253</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>7838</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>19432</t>
+          <t>18878</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>16,85%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>114224</t>
+          <t>114532</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>127058</t>
+          <t>127150</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>83,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>121545</t>
+          <t>121319</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>134068</t>
+          <t>134369</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>240075</t>
+          <t>241119</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>257999</t>
+          <t>258260</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,99%</t>
         </is>
       </c>
     </row>
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10316</t>
+          <t>10224</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>23150</t>
+          <t>22842</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>9296</t>
+          <t>8995</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>21819</t>
+          <t>22045</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>22739</t>
+          <t>22478</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>40663</t>
+          <t>39619</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,11%</t>
         </is>
       </c>
     </row>
@@ -6455,12 +6455,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>143232</t>
+          <t>143146</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>154470</t>
+          <t>154628</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>147757</t>
+          <t>146904</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>159295</t>
+          <t>159098</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>294524</t>
+          <t>294474</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>311435</t>
+          <t>310604</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,38%</t>
         </is>
       </c>
     </row>
@@ -6568,12 +6568,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8577</t>
+          <t>8419</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>19815</t>
+          <t>19901</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>10295</t>
+          <t>10492</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>21833</t>
+          <t>22686</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>21202</t>
+          <t>22033</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>38113</t>
+          <t>38163</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6653,12 +6653,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,47%</t>
         </is>
       </c>
     </row>
@@ -6798,12 +6798,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>624673</t>
+          <t>626864</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>649068</t>
+          <t>649469</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>668091</t>
+          <t>668554</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>692183</t>
+          <t>691154</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6868,12 +6868,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1300595</t>
+          <t>1297779</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1333907</t>
+          <t>1333413</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,73%</t>
         </is>
       </c>
     </row>
@@ -6911,12 +6911,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>50824</t>
+          <t>50423</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>75219</t>
+          <t>73028</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>45900</t>
+          <t>46929</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>69992</t>
+          <t>69529</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>104068</t>
+          <t>104562</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>137380</t>
+          <t>140196</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP04F-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP04F-Provincia-trans_orig.xlsx
@@ -542,7 +542,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -553,7 +553,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -721,72 +721,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>57538</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>52077</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>60916</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>88,78%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>80,36%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>93,99%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>46465</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>41101</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>50162</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>41602</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>50301</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>83,42%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>73,79%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>90,06%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>57538</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>52408</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>61317</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>88,78%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>74,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>96888</t>
+          <t>97119</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>109485</t>
+          <t>109820</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>91,13%</t>
         </is>
       </c>
     </row>
@@ -834,72 +834,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>7271</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3893</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>12732</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>11,22%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>6,01%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>19,64%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>9235</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5538</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>14599</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>5399</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>14098</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>16,58%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>9,94%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>26,21%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>7271</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>3492</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>12401</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>11,22%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11024</t>
+          <t>10689</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23621</t>
+          <t>23390</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,41%</t>
         </is>
       </c>
     </row>
@@ -947,57 +947,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>64809</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>64809</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>64809</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>55700</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>55700</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>55700</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>64809</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>64809</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>64809</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1064,72 +1064,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>105095</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>100583</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>108216</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>94,54%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>90,49%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>97,35%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>97202</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>92004</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>100799</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>91326</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>100728</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>92,83%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>87,86%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>96,26%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>105095</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>100069</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>108003</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>94,54%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>195678</t>
+          <t>195659</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>207481</t>
+          <t>207234</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,0%</t>
         </is>
       </c>
     </row>
@@ -1177,72 +1177,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6064</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2943</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>10576</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>5,46%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2,65%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>9,51%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>7511</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3914</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>12709</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>3985</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>13387</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>7,17%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3,74%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>12,14%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>6064</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>3156</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>11090</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>5,46%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>8391</t>
+          <t>8638</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>20194</t>
+          <t>20213</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -1290,57 +1290,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>104713</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>104713</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>104713</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1407,72 +1407,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>63816</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>59202</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>67246</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>89,56%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>83,09%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>94,38%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>59614</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>54340</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>63747</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>54656</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>63880</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>87,44%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>79,7%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>93,5%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>63816</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>58802</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>67238</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>89,56%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>80,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>116123</t>
+          <t>116559</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>128921</t>
+          <t>129025</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,54%</t>
         </is>
       </c>
     </row>
@@ -1520,72 +1520,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>7438</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4008</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>12052</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>10,44%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>5,62%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>16,91%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>8564</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>4431</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>13838</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>4298</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>13522</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>12,56%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>6,5%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>20,3%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>7438</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>4016</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>12452</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>10,44%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10511</t>
+          <t>10407</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>23309</t>
+          <t>22873</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,4%</t>
         </is>
       </c>
     </row>
@@ -1633,57 +1633,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>71254</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>71254</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>71254</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>68178</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>68178</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>68178</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>71254</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>71254</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>71254</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1750,72 +1750,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>79643</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>76179</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>81144</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>97,36%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>93,12%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>99,19%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>107</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>72455</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>67109</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>75459</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>68034</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>75495</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>93,18%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>86,3%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>97,04%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>79643</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>75117</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>81144</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>97,36%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>146194</t>
+          <t>146406</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>155717</t>
+          <t>155883</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,69%</t>
         </is>
       </c>
     </row>
@@ -1863,72 +1863,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2162</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>661</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5626</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2,64%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>6,88%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>5306</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>2302</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>10652</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>2266</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>9727</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>6,82%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2,96%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>13,7%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>2162</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>661</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>6688</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>2,64%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3849</t>
+          <t>3683</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13372</t>
+          <t>13160</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,25%</t>
         </is>
       </c>
     </row>
@@ -1976,57 +1976,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>81805</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>81805</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>81805</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>77761</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>77761</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>77761</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>81805</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>81805</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>81805</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2093,72 +2093,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>41604</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>37311</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>44642</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>88,99%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>79,81%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>95,49%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>39694</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>35625</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>42495</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>35605</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>41884</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>90,42%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>81,15%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>96,8%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>41604</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>36639</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>44278</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>88,99%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>75767</t>
+          <t>75691</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>85420</t>
+          <t>85503</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,32%</t>
         </is>
       </c>
     </row>
@@ -2206,72 +2206,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>5148</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2110</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>9441</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>11,01%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>4,51%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>20,19%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>4207</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>1406</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>8276</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>8296</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>9,58%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>3,2%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>18,85%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>5148</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>2474</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>10113</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>11,01%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5233</t>
+          <t>5150</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14886</t>
+          <t>14962</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,5%</t>
         </is>
       </c>
     </row>
@@ -2319,57 +2319,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>46752</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>46752</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>46752</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>43901</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>43901</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>43901</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>46752</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>46752</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>46752</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2436,72 +2436,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>54978</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>50656</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>57394</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>92,46%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>85,2%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>96,53%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>48939</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>44208</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>52347</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>44588</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>52383</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>88,51%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>79,96%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>94,68%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>54978</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>50335</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>57454</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>92,46%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>80,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>98145</t>
+          <t>98373</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>108746</t>
+          <t>108514</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,57%</t>
         </is>
       </c>
     </row>
@@ -2549,72 +2549,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>4480</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2064</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>8802</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>7,54%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>3,47%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>14,8%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>6352</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>2944</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>11083</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>2908</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>10703</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>11,49%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>5,32%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>20,04%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>4480</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>9123</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>7,54%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6003</t>
+          <t>6235</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>16604</t>
+          <t>16376</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,27%</t>
         </is>
       </c>
     </row>
@@ -2662,57 +2662,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>59458</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>59458</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>59458</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>55291</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>55291</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>55291</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>59458</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>59458</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>59458</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2779,72 +2779,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>130731</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>123548</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>135566</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>90,52%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>85,55%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>93,87%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>172</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>123073</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>116315</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>128419</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>115976</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>128413</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>89,81%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>84,88%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>93,71%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>130731</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>124438</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>135709</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>90,52%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>245137</t>
+          <t>244301</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>260837</t>
+          <t>260752</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,64%</t>
         </is>
       </c>
     </row>
@@ -2897,67 +2897,67 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t>13692</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>8857</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>20875</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>9,48%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>6,13%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>14,45%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
           <t>13968</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>8622</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>20726</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>8628</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>21065</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>10,19%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>6,29%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>15,12%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>13692</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>8714</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>19985</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>9,48%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>20627</t>
+          <t>20712</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>36327</t>
+          <t>37163</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,2%</t>
         </is>
       </c>
     </row>
@@ -3005,57 +3005,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>144423</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>144423</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>144423</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>137041</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>137041</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>137041</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>144423</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>144423</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>144423</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3122,72 +3122,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>148928</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>140102</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>155012</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>87,65%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>82,46%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>91,23%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>217</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>143466</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>135386</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>149140</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>136335</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>149413</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>88,86%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>83,86%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>92,37%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>148928</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>140901</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>155499</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>87,65%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>281051</t>
+          <t>282267</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>300665</t>
+          <t>301020</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,84%</t>
         </is>
       </c>
     </row>
@@ -3235,72 +3235,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>20979</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>14895</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>29805</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>12,35%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>8,77%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>17,54%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>17986</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>12312</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>26066</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>12039</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>25117</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>11,14%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>7,63%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>16,14%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>20979</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>14408</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>29006</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>12,35%</t>
-        </is>
-      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>30694</t>
+          <t>30339</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>50308</t>
+          <t>49092</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>14,82%</t>
         </is>
       </c>
     </row>
@@ -3348,57 +3348,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>169907</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>169907</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>169907</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>161452</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>161452</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>161452</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>169907</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>169907</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>169907</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3465,72 +3465,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>973</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>682333</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>668068</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>694133</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>91,03%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>89,13%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>92,6%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>911</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>630907</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>616498</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>642454</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>617404</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>643024</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>89,61%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>87,57%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>91,25%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>973</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>682333</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>668705</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>694298</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>91,03%</t>
-        </is>
-      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1292995</t>
+          <t>1291404</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1330131</t>
+          <t>1331029</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3560,12 +3560,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,57%</t>
         </is>
       </c>
     </row>
@@ -3578,72 +3578,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>67235</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>55435</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>81500</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>8,97%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>7,4%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>10,87%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>73130</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>61583</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>87539</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>61013</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>86633</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>10,39%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>8,75%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>12,43%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>67235</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>55270</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>80863</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>8,97%</t>
-        </is>
-      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>123474</t>
+          <t>122576</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>160610</t>
+          <t>162201</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -3691,57 +3691,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>1068</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>749568</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>749568</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>749568</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>1016</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>704037</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>704037</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>704037</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>1068</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>749568</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>749568</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>749568</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3865,7 +3865,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3876,7 +3876,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4044,72 +4044,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>56169</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>50926</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>59675</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>87,14%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>79,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>92,57%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>48656</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>44075</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>51917</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>44021</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>52148</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>86,34%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>78,21%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>92,13%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>56169</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>51103</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>59695</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>87,14%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>78,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>97837</t>
+          <t>98197</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>110042</t>
+          <t>110173</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,19%</t>
         </is>
       </c>
     </row>
@@ -4162,67 +4162,67 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>8293</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4787</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>13536</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>12,86%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>7,43%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>21,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>7697</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>4436</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>12278</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>4205</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>12332</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>13,66%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>7,87%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>21,79%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>8293</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>4767</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>13359</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>12,86%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10773</t>
+          <t>10642</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22978</t>
+          <t>22618</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,72%</t>
         </is>
       </c>
     </row>
@@ -4270,57 +4270,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>56353</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>56353</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>56353</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4387,72 +4387,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>104732</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>100113</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>106861</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>96,83%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>92,56%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>98,79%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>150</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>99272</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>94998</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>101725</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>94128</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>101765</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>96,06%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>91,92%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>98,43%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>104732</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>100608</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>106838</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>96,83%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>198645</t>
+          <t>198336</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>207597</t>
+          <t>207463</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,09%</t>
         </is>
       </c>
     </row>
@@ -4500,72 +4500,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3434</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1305</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>8053</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>3,17%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1,21%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>7,44%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>4071</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1618</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>8345</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1578</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>9215</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>3,94%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>8,08%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>3434</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>1328</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>7558</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>3,17%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3912</t>
+          <t>4046</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12864</t>
+          <t>13173</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -4613,57 +4613,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>108166</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>108166</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>108166</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>103343</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>103343</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>103343</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>108166</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>108166</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>108166</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4730,74 +4730,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>63942</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>58244</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>67065</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>91,47%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>83,32%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>95,94%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>63014</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>58256</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>65375</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>58575</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>65371</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>94,29%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>87,17%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>87,65%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>97,82%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>63942</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>58875</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>67025</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>91,47%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>84,22%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>95,88%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>174</t>
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>119460</t>
+          <t>120716</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>130882</t>
+          <t>130746</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,62%</t>
         </is>
       </c>
     </row>
@@ -4843,72 +4843,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>5963</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2840</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>11661</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>8,53%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>4,06%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>16,68%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>3817</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1456</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>8575</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>1460</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>8256</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>5,71%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>2,18%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>12,83%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>5963</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>2880</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>11030</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>8,53%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>4,12%</t>
-        </is>
-      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5854</t>
+          <t>5990</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>17276</t>
+          <t>16020</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>11,72%</t>
         </is>
       </c>
     </row>
@@ -4956,57 +4956,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>66831</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>66831</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>66831</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>76357</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>72171</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>78455</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>96,45%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>91,16%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>99,1%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>102</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>70582</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>65966</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>73323</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>66299</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>73244</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>93,11%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>87,02%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>96,72%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>76357</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>72139</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>78434</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>96,45%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>141110</t>
+          <t>141601</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>150779</t>
+          <t>150845</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,33%</t>
         </is>
       </c>
     </row>
@@ -5186,72 +5186,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2812</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>714</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>6998</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>3,55%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>8,84%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>5226</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>2485</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>9842</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>2564</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>9509</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>6,89%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>3,28%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>12,98%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>2812</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>735</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>7030</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>3,55%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4198</t>
+          <t>4132</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13867</t>
+          <t>13376</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -5299,57 +5299,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>79169</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>79169</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>79169</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>75808</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>75808</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>75808</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>79169</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>79169</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>79169</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>42559</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>38651</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>44544</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>93,15%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>84,6%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>97,5%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>39381</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>35023</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>41530</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>35583</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>41534</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>91,88%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>81,71%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>96,89%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>42559</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>38707</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>44509</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>93,15%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>76631</t>
+          <t>76290</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>85208</t>
+          <t>84848</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>95,82%</t>
         </is>
       </c>
     </row>
@@ -5534,67 +5534,67 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>3129</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1144</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>7037</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>6,85%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>15,4%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
           <t>3482</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>1333</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>7840</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>1329</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>7280</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>8,12%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>3,11%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>18,29%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>3129</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>1179</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>6981</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>6,85%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3343</t>
+          <t>3703</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11920</t>
+          <t>12261</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,85%</t>
         </is>
       </c>
     </row>
@@ -5642,57 +5642,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>45688</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>45688</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>45688</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>42863</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>42863</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>42863</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>45688</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>45688</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>45688</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>53944</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>49728</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>56259</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>93,43%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>86,13%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>97,44%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>45637</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>40877</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>49394</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>40464</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>49337</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>84,09%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>75,32%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>91,01%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>53944</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>49486</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>56298</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>93,43%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>93134</t>
+          <t>93097</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>104174</t>
+          <t>104492</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>93,29%</t>
         </is>
       </c>
     </row>
@@ -5872,72 +5872,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3795</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1480</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>8011</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>6,57%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>2,56%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>13,87%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>8636</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>4879</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>13396</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>4936</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>13809</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>15,91%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>8,99%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>24,68%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>3795</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>1441</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>8253</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>6,57%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>7838</t>
+          <t>7520</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>18878</t>
+          <t>18915</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,89%</t>
         </is>
       </c>
     </row>
@@ -5985,57 +5985,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>54273</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>54273</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>54273</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>128740</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>121685</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>134033</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>89,8%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>84,88%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>93,49%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>121473</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>114532</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>127150</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>113454</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>126718</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>88,42%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>83,37%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>92,56%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>128740</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>121319</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>134369</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>89,8%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>241119</t>
+          <t>240524</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>258260</t>
+          <t>258436</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,06%</t>
         </is>
       </c>
     </row>
@@ -6215,72 +6215,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>14624</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>9331</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>21679</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>10,2%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>6,51%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>15,12%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>15901</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>10224</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>22842</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>10656</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>23920</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>11,58%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>7,44%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>16,63%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>14624</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>8995</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>22045</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>10,2%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>22478</t>
+          <t>22302</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>39619</t>
+          <t>40214</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,32%</t>
         </is>
       </c>
     </row>
@@ -6333,52 +6333,52 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>143364</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>143364</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>143364</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
           <t>137374</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>137374</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>137374</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>143364</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>143364</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>143364</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6445,72 +6445,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>154023</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>146775</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>159454</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>90,82%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>86,55%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>94,02%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>237</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>149582</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>143146</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>154628</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>143425</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>154347</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>91,74%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>87,79%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>94,84%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>154023</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>146904</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>159098</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>90,82%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>294474</t>
+          <t>294949</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>310604</t>
+          <t>311132</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,53%</t>
         </is>
       </c>
     </row>
@@ -6558,72 +6558,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>15567</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>10136</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>22815</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>9,18%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>5,98%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>13,45%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>13465</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>8419</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>19901</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>8700</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>19622</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>8,26%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>5,16%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>12,21%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>15567</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>10492</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>22686</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>9,18%</t>
-        </is>
-      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>22033</t>
+          <t>21505</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>38163</t>
+          <t>37688</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6653,12 +6653,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,33%</t>
         </is>
       </c>
     </row>
@@ -6671,57 +6671,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>169590</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>169590</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>169590</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>163047</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>163047</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>163047</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>169590</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>169590</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>169590</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6788,72 +6788,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>970</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>680466</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>667569</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>690857</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>92,19%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>90,45%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>93,6%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>959</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>637596</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>626864</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>649469</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>623377</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>647722</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>91,1%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>89,57%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>92,8%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>970</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>680466</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>668554</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>691154</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>92,19%</t>
-        </is>
-      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6868,12 +6868,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1297779</t>
+          <t>1298023</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1333413</t>
+          <t>1334574</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,81%</t>
         </is>
       </c>
     </row>
@@ -6901,72 +6901,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>57617</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>47226</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>70514</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>7,81%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>6,4%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>9,55%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>62296</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>50423</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>73028</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>52170</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>76515</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>8,9%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>7,2%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>10,43%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>57617</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>46929</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>69529</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>7,81%</t>
-        </is>
-      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>104562</t>
+          <t>103401</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>140196</t>
+          <t>139952</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -7014,57 +7014,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>1055</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>738083</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>738083</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>738083</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>1053</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>699892</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>699892</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>699892</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>1055</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>738083</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>738083</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>738083</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
